--- a/artfynd/A 52653-2024 artfynd.xlsx
+++ b/artfynd/A 52653-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121257427</v>
       </c>
       <c r="B2" t="n">
-        <v>100337</v>
+        <v>100347</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121257415</v>
+        <v>121260328</v>
       </c>
       <c r="B3" t="n">
-        <v>90125</v>
+        <v>91093</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,45 +803,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2008</v>
+        <v>4217</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fyrflikig jordstjärna</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Geastrum quadrifidum</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kastkärret, Kastkärret, Srm</t>
+          <t>Kastkärret, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>607630</v>
+        <v>607778</v>
       </c>
       <c r="R3" t="n">
-        <v>6535481</v>
+        <v>6535602</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,19 +867,9 @@
           <t>2024-11-19</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>12:18</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-11-19</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>12:18</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,28 +878,34 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
+          <t>Rolf Olsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Göran Ekström, Rolf Olsson</t>
+          <t>Rolf Olsson, Göran Ekström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121260328</v>
+        <v>121257415</v>
       </c>
       <c r="B4" t="n">
-        <v>91083</v>
+        <v>90135</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -922,41 +914,45 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4217</v>
+        <v>2008</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Geastrum quadrifidum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>Pers.:Pers.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kastkärret, Srm</t>
+          <t>Kastkärret, Kastkärret, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>607778</v>
+        <v>607630</v>
       </c>
       <c r="R4" t="n">
-        <v>6535602</v>
+        <v>6535481</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,9 +982,19 @@
           <t>2024-11-19</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-11-19</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -997,24 +1003,18 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
-      </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Rolf Olsson</t>
+          <t>Göran Ekström</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Rolf Olsson, Göran Ekström</t>
+          <t>Göran Ekström, Rolf Olsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 52653-2024 artfynd.xlsx
+++ b/artfynd/A 52653-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121257427</v>
+        <v>121257415</v>
       </c>
       <c r="B2" t="n">
-        <v>100347</v>
+        <v>90135</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,34 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>2008</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Geastrum quadrifidum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>Pers.:Pers.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,13 +722,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>607619</v>
+        <v>607630</v>
       </c>
       <c r="R2" t="n">
-        <v>6535515</v>
+        <v>6535481</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,7 +757,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +767,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -902,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121257415</v>
+        <v>121257427</v>
       </c>
       <c r="B4" t="n">
-        <v>90135</v>
+        <v>100347</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -914,34 +917,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2008</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fyrflikig jordstjärna</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Geastrum quadrifidum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -949,13 +949,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>607630</v>
+        <v>607619</v>
       </c>
       <c r="R4" t="n">
-        <v>6535481</v>
+        <v>6535515</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 52653-2024 artfynd.xlsx
+++ b/artfynd/A 52653-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121257415</v>
+        <v>121260328</v>
       </c>
       <c r="B2" t="n">
-        <v>90135</v>
+        <v>91105</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,45 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2008</v>
+        <v>4217</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fyrflikig jordstjärna</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Geastrum quadrifidum</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kastkärret, Kastkärret, Srm</t>
+          <t>Kastkärret, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>607630</v>
+        <v>607778</v>
       </c>
       <c r="R2" t="n">
-        <v>6535481</v>
+        <v>6535602</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,19 +751,9 @@
           <t>2024-11-19</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>12:18</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-11-19</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>12:18</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,28 +762,34 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
+          <t>Rolf Olsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Göran Ekström, Rolf Olsson</t>
+          <t>Rolf Olsson, Göran Ekström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121260328</v>
+        <v>121257415</v>
       </c>
       <c r="B3" t="n">
-        <v>91093</v>
+        <v>90143</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,41 +798,45 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4217</v>
+        <v>2008</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Geastrum quadrifidum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>Pers.:Pers.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kastkärret, Srm</t>
+          <t>Kastkärret, Kastkärret, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>607778</v>
+        <v>607630</v>
       </c>
       <c r="R3" t="n">
-        <v>6535602</v>
+        <v>6535481</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,9 +866,19 @@
           <t>2024-11-19</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-11-19</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -881,24 +887,18 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
-      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Rolf Olsson</t>
+          <t>Göran Ekström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Rolf Olsson, Göran Ekström</t>
+          <t>Göran Ekström, Rolf Olsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -908,7 +908,7 @@
         <v>121257427</v>
       </c>
       <c r="B4" t="n">
-        <v>100347</v>
+        <v>100360</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 52653-2024 artfynd.xlsx
+++ b/artfynd/A 52653-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121260328</v>
+        <v>121257427</v>
       </c>
       <c r="B2" t="n">
-        <v>91105</v>
+        <v>100361</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,40 +691,41 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4217</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kastkärret, Srm</t>
+          <t>Kastkärret, Kastkärret, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>607778</v>
+        <v>607619</v>
       </c>
       <c r="R2" t="n">
-        <v>6535602</v>
+        <v>6535515</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -751,9 +752,19 @@
           <t>2024-11-19</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-11-19</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -762,24 +773,18 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Rolf Olsson</t>
+          <t>Göran Ekström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Rolf Olsson, Göran Ekström</t>
+          <t>Göran Ekström, Rolf Olsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -789,7 +794,7 @@
         <v>121257415</v>
       </c>
       <c r="B3" t="n">
-        <v>90143</v>
+        <v>90144</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -905,10 +910,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121257427</v>
+        <v>121260328</v>
       </c>
       <c r="B4" t="n">
-        <v>100360</v>
+        <v>91106</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,41 +926,40 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>4217</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kastkärret, Kastkärret, Srm</t>
+          <t>Kastkärret, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>607619</v>
+        <v>607778</v>
       </c>
       <c r="R4" t="n">
-        <v>6535515</v>
+        <v>6535602</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -982,19 +986,9 @@
           <t>2024-11-19</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>13:39</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-11-19</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>13:39</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1003,18 +997,24 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
+          <t>Rolf Olsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Göran Ekström, Rolf Olsson</t>
+          <t>Rolf Olsson, Göran Ekström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 52653-2024 artfynd.xlsx
+++ b/artfynd/A 52653-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121257427</v>
       </c>
       <c r="B2" t="n">
-        <v>100361</v>
+        <v>100364</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121257415</v>
+        <v>121260328</v>
       </c>
       <c r="B3" t="n">
-        <v>90144</v>
+        <v>91109</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,45 +803,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2008</v>
+        <v>4217</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fyrflikig jordstjärna</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Geastrum quadrifidum</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kastkärret, Kastkärret, Srm</t>
+          <t>Kastkärret, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>607630</v>
+        <v>607778</v>
       </c>
       <c r="R3" t="n">
-        <v>6535481</v>
+        <v>6535602</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,19 +867,9 @@
           <t>2024-11-19</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>12:18</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-11-19</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>12:18</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,28 +878,34 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
+          <t>Rolf Olsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Göran Ekström, Rolf Olsson</t>
+          <t>Rolf Olsson, Göran Ekström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121260328</v>
+        <v>121257415</v>
       </c>
       <c r="B4" t="n">
-        <v>91106</v>
+        <v>90147</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -922,41 +914,45 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4217</v>
+        <v>2008</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Geastrum quadrifidum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>Pers.:Pers.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kastkärret, Srm</t>
+          <t>Kastkärret, Kastkärret, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>607778</v>
+        <v>607630</v>
       </c>
       <c r="R4" t="n">
-        <v>6535602</v>
+        <v>6535481</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,9 +982,19 @@
           <t>2024-11-19</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-11-19</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -997,24 +1003,18 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
-      </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Rolf Olsson</t>
+          <t>Göran Ekström</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Rolf Olsson, Göran Ekström</t>
+          <t>Göran Ekström, Rolf Olsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 52653-2024 artfynd.xlsx
+++ b/artfynd/A 52653-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121257427</v>
+        <v>121257415</v>
       </c>
       <c r="B2" t="n">
-        <v>100364</v>
+        <v>90153</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,34 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>2008</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Geastrum quadrifidum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>Pers.:Pers.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,13 +722,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>607619</v>
+        <v>607630</v>
       </c>
       <c r="R2" t="n">
-        <v>6535515</v>
+        <v>6535481</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,7 +757,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +767,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121260328</v>
+        <v>121257427</v>
       </c>
       <c r="B3" t="n">
-        <v>91109</v>
+        <v>100370</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,40 +810,41 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4217</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kastkärret, Srm</t>
+          <t>Kastkärret, Kastkärret, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>607778</v>
+        <v>607619</v>
       </c>
       <c r="R3" t="n">
-        <v>6535602</v>
+        <v>6535515</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,9 +871,19 @@
           <t>2024-11-19</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-11-19</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -878,34 +892,28 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
-      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Rolf Olsson</t>
+          <t>Göran Ekström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Rolf Olsson, Göran Ekström</t>
+          <t>Göran Ekström, Rolf Olsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121257415</v>
+        <v>121260328</v>
       </c>
       <c r="B4" t="n">
-        <v>90147</v>
+        <v>91115</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -914,45 +922,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2008</v>
+        <v>4217</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fyrflikig jordstjärna</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Geastrum quadrifidum</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kastkärret, Kastkärret, Srm</t>
+          <t>Kastkärret, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>607630</v>
+        <v>607778</v>
       </c>
       <c r="R4" t="n">
-        <v>6535481</v>
+        <v>6535602</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,19 +986,9 @@
           <t>2024-11-19</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>12:18</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-11-19</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>12:18</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1003,18 +997,24 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
+          <t>Rolf Olsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Göran Ekström, Rolf Olsson</t>
+          <t>Rolf Olsson, Göran Ekström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 52653-2024 artfynd.xlsx
+++ b/artfynd/A 52653-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121257415</v>
+        <v>121257427</v>
       </c>
       <c r="B2" t="n">
-        <v>90153</v>
+        <v>100371</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,34 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2008</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fyrflikig jordstjärna</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Geastrum quadrifidum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -722,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>607630</v>
+        <v>607619</v>
       </c>
       <c r="R2" t="n">
-        <v>6535481</v>
+        <v>6535515</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -767,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121257427</v>
+        <v>121257415</v>
       </c>
       <c r="B3" t="n">
-        <v>100370</v>
+        <v>90154</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,31 +803,34 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>2008</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Geastrum quadrifidum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>Pers.:Pers.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -838,13 +838,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>607619</v>
+        <v>607630</v>
       </c>
       <c r="R3" t="n">
-        <v>6535515</v>
+        <v>6535481</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -913,7 +913,7 @@
         <v>121260328</v>
       </c>
       <c r="B4" t="n">
-        <v>91115</v>
+        <v>91116</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 52653-2024 artfynd.xlsx
+++ b/artfynd/A 52653-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121257427</v>
+        <v>121260328</v>
       </c>
       <c r="B2" t="n">
-        <v>100371</v>
+        <v>91116</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,41 +691,40 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>4217</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kastkärret, Kastkärret, Srm</t>
+          <t>Kastkärret, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>607619</v>
+        <v>607778</v>
       </c>
       <c r="R2" t="n">
-        <v>6535515</v>
+        <v>6535602</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -752,19 +751,9 @@
           <t>2024-11-19</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>13:39</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-11-19</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>13:39</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -773,18 +762,24 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
+          <t>Rolf Olsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Göran Ekström, Rolf Olsson</t>
+          <t>Rolf Olsson, Göran Ekström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -910,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121260328</v>
+        <v>121257427</v>
       </c>
       <c r="B4" t="n">
-        <v>91116</v>
+        <v>100371</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -926,40 +921,41 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4217</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kastkärret, Srm</t>
+          <t>Kastkärret, Kastkärret, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>607778</v>
+        <v>607619</v>
       </c>
       <c r="R4" t="n">
-        <v>6535602</v>
+        <v>6535515</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -986,9 +982,19 @@
           <t>2024-11-19</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-11-19</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -997,24 +1003,18 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
-      </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Rolf Olsson</t>
+          <t>Göran Ekström</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Rolf Olsson, Göran Ekström</t>
+          <t>Göran Ekström, Rolf Olsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 52653-2024 artfynd.xlsx
+++ b/artfynd/A 52653-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121260328</v>
+        <v>121257427</v>
       </c>
       <c r="B2" t="n">
-        <v>91116</v>
+        <v>100371</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,40 +691,41 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4217</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kastkärret, Srm</t>
+          <t>Kastkärret, Kastkärret, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>607778</v>
+        <v>607619</v>
       </c>
       <c r="R2" t="n">
-        <v>6535602</v>
+        <v>6535515</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -751,9 +752,19 @@
           <t>2024-11-19</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-11-19</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -762,34 +773,28 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Rolf Olsson</t>
+          <t>Göran Ekström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Rolf Olsson, Göran Ekström</t>
+          <t>Göran Ekström, Rolf Olsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121257415</v>
+        <v>121260328</v>
       </c>
       <c r="B3" t="n">
-        <v>90154</v>
+        <v>91116</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,45 +803,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2008</v>
+        <v>4217</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fyrflikig jordstjärna</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Geastrum quadrifidum</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kastkärret, Kastkärret, Srm</t>
+          <t>Kastkärret, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>607630</v>
+        <v>607778</v>
       </c>
       <c r="R3" t="n">
-        <v>6535481</v>
+        <v>6535602</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,19 +867,9 @@
           <t>2024-11-19</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>12:18</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-11-19</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>12:18</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,28 +878,34 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
+          <t>Rolf Olsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Göran Ekström, Rolf Olsson</t>
+          <t>Rolf Olsson, Göran Ekström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121257427</v>
+        <v>121257415</v>
       </c>
       <c r="B4" t="n">
-        <v>100371</v>
+        <v>90154</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -917,31 +914,34 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>2008</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Geastrum quadrifidum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>Pers.:Pers.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -949,13 +949,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>607619</v>
+        <v>607630</v>
       </c>
       <c r="R4" t="n">
-        <v>6535515</v>
+        <v>6535481</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 52653-2024 artfynd.xlsx
+++ b/artfynd/A 52653-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121257427</v>
+        <v>121260328</v>
       </c>
       <c r="B2" t="n">
-        <v>100371</v>
+        <v>91116</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,41 +691,40 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>4217</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kastkärret, Kastkärret, Srm</t>
+          <t>Kastkärret, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>607619</v>
+        <v>607778</v>
       </c>
       <c r="R2" t="n">
-        <v>6535515</v>
+        <v>6535602</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -752,19 +751,9 @@
           <t>2024-11-19</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>13:39</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-11-19</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>13:39</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -773,28 +762,34 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
+          <t>Rolf Olsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Göran Ekström, Rolf Olsson</t>
+          <t>Rolf Olsson, Göran Ekström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121260328</v>
+        <v>121257427</v>
       </c>
       <c r="B3" t="n">
-        <v>91116</v>
+        <v>100371</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,40 +802,41 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4217</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kastkärret, Srm</t>
+          <t>Kastkärret, Kastkärret, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>607778</v>
+        <v>607619</v>
       </c>
       <c r="R3" t="n">
-        <v>6535602</v>
+        <v>6535515</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,9 +863,19 @@
           <t>2024-11-19</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-11-19</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -878,24 +884,18 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
-      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Rolf Olsson</t>
+          <t>Göran Ekström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Rolf Olsson, Göran Ekström</t>
+          <t>Göran Ekström, Rolf Olsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
